--- a/data/trans_camb/IP19C06-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP19C06-Estudios-trans_camb.xlsx
@@ -687,7 +687,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,06</t>
+          <t>0,0; 14,11</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -697,7 +697,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,39</t>
+          <t>0,0; 12,14</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -712,12 +712,12 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,04</t>
+          <t>0,0; 7,9</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,22</t>
+          <t>0,0; 6,85</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,58; 3,36</t>
+          <t>0,57; 3,49</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,82</t>
+          <t>0,0; 2,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,16; 1,85</t>
+          <t>0,16; 1,91</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,38; 1,54</t>
+          <t>-0,28; 1,68</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,23; 0,0</t>
+          <t>-1,08; 0,0</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,43; 1,7</t>
+          <t>-0,43; 1,57</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,3; 2,07</t>
+          <t>0,22; 1,9</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-0,18; 0,82</t>
+          <t>-0,11; 0,78</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-0,02; 1,18</t>
+          <t>-0,01; 1,28</t>
         </is>
       </c>
     </row>
@@ -1119,37 +1119,37 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,18; 7,47</t>
+          <t>1,07; 7,42</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,89; 1,83</t>
+          <t>-2,89; 1,86</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-6,18; 0,0</t>
+          <t>-4,72; 0,0</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-2,87; 1,57</t>
+          <t>-3,78; 1,57</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-1,43; 0,9</t>
+          <t>-1,71; 0,89</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-2,66; 0,0</t>
+          <t>-2,59; 0,0</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-0,21; 3,4</t>
+          <t>-0,28; 3,34</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,32; 2,0</t>
+          <t>0,32; 2,07</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,49</t>
+          <t>0,0; 1,28</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,73; 2,66</t>
+          <t>0,68; 2,68</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,44; 1,35</t>
+          <t>-0,48; 1,32</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,82; 0,38</t>
+          <t>-0,86; 0,38</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,45; 1,17</t>
+          <t>-0,51; 1,22</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,11; 1,21</t>
+          <t>0,1; 1,26</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-0,24; 0,59</t>
+          <t>-0,21; 0,55</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,21; 1,42</t>
+          <t>0,22; 1,5</t>
         </is>
       </c>
     </row>
@@ -1461,7 +1461,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-61,01; —</t>
+          <t>-38,5; —</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-8,7; —</t>
+          <t>-13,05; —</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP19C06-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP19C06-Estudios-trans_camb.xlsx
@@ -687,7 +687,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,11</t>
+          <t>0,0; 12,08</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -697,7 +697,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,14</t>
+          <t>0,0; 10,98</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -712,12 +712,12 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,9</t>
+          <t>0,0; 6,94</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,85</t>
+          <t>0,0; 6,36</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,57; 3,49</t>
+          <t>0,51; 3,35</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,0</t>
+          <t>0,0; 1,95</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,16; 1,91</t>
+          <t>0,16; 1,83</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,28; 1,68</t>
+          <t>-0,22; 1,61</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,08; 0,0</t>
+          <t>-1,29; 0,0</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,43; 1,57</t>
+          <t>-0,43; 1,66</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,22; 1,9</t>
+          <t>0,31; 1,99</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-0,11; 0,78</t>
+          <t>-0,18; 0,84</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-0,01; 1,28</t>
+          <t>-0,07; 1,32</t>
         </is>
       </c>
     </row>
@@ -1119,37 +1119,37 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,07; 7,42</t>
+          <t>1,17; 7,81</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,89; 1,86</t>
+          <t>-2,9; 1,81</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-4,72; 0,0</t>
+          <t>-4,54; 0,0</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-3,78; 1,57</t>
+          <t>-3,64; 1,56</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-1,71; 0,89</t>
+          <t>-1,42; 0,91</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-2,59; 0,0</t>
+          <t>-2,69; 0,0</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-0,28; 3,34</t>
+          <t>-0,11; 3,41</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,32; 2,07</t>
+          <t>0,32; 2,06</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,28</t>
+          <t>0,0; 1,37</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,68; 2,68</t>
+          <t>0,71; 2,83</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,48; 1,32</t>
+          <t>-0,46; 1,3</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,86; 0,38</t>
+          <t>-0,87; 0,38</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 1,22</t>
+          <t>-0,53; 1,19</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,1; 1,26</t>
+          <t>0,1; 1,28</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-0,21; 0,55</t>
+          <t>-0,24; 0,59</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,22; 1,5</t>
+          <t>0,2; 1,53</t>
         </is>
       </c>
     </row>
@@ -1461,7 +1461,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-38,5; —</t>
+          <t>-57,42; —</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-13,05; —</t>
+          <t>-19,06; —</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP19C06-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP19C06-Estudios-trans_camb.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -629,14 +629,14 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>2,49</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>0,0</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>2,5</t>
-        </is>
-      </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
           <t>0,0</t>
@@ -644,19 +644,19 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>2,49</t>
+          <t>0,0</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
+          <t>3,01</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
           <t>0,0</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
           <t>1,39</t>
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>1,35</t>
+          <t>1,58</t>
         </is>
       </c>
     </row>
@@ -682,12 +682,12 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 10,39</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,08</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -697,12 +697,12 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,98</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 13,08</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -712,12 +712,12 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,94</t>
+          <t>0,0; 7,04</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,36</t>
+          <t>0,0; 8,01</t>
         </is>
       </c>
     </row>
@@ -735,27 +735,27 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
+          <t>inf%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>inf%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>0,4</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-0,21</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>-0,01</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>1,46</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>0,55</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>0,63</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>0,4</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-0,21</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,2</t>
+          <t>0,57</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>0,4</t>
+          <t>0,26</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,51; 3,35</t>
+          <t>-0,38; 1,54</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,95</t>
+          <t>-1,23; 0,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,16; 1,83</t>
+          <t>-0,65; 0,43</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,22; 1,61</t>
+          <t>0,58; 3,36</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,29; 0,0</t>
+          <t>0,0; 1,82</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,43; 1,66</t>
+          <t>0,14; 1,7</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,31; 1,99</t>
+          <t>0,3; 2,07</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-0,18; 0,84</t>
+          <t>-0,18; 0,82</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-0,07; 1,32</t>
+          <t>-0,09; 0,79</t>
         </is>
       </c>
     </row>
@@ -946,34 +946,34 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>187,89%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>-3,07%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>inf%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>inf%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>inf%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>187,89%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>93,13%</t>
-        </is>
-      </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
           <t>822,45%</t>
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>360,36%</t>
+          <t>239,09%</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>-0,05</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>-0,95</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>-0,19</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>0,0</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>0,0</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>3,36</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-0,05</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-0,95</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-0,18</t>
+          <t>3,25</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1,4</t>
+          <t>1,41</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-2,89; 1,83</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-6,18; 0,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,17; 7,81</t>
+          <t>-2,87; 1,56</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,9; 1,81</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-4,54; 0,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-3,64; 1,56</t>
+          <t>1,11; 7,34</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-1,42; 0,91</t>
+          <t>-1,43; 0,9</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-2,69; 0,0</t>
+          <t>-2,66; 0,0</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-0,11; 3,41</t>
+          <t>-0,23; 3,44</t>
         </is>
       </c>
     </row>
@@ -1162,47 +1162,47 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>-4,95%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>-20,26%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>inf%</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-4,95%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>-5,25%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
         <is>
           <t>-100,0%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>-19,1%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>-5,25%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>300,2%</t>
+          <t>301,82%</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>0,27</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-0,15</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>0,01</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>0,91</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>0,38</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>1,47</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>0,27</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>-0,15</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,15</t>
+          <t>1,44</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>0,76</t>
+          <t>0,68</t>
         </is>
       </c>
     </row>
@@ -1325,37 +1325,37 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,32; 2,06</t>
+          <t>-0,44; 1,35</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,37</t>
+          <t>-0,82; 0,38</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,71; 2,83</t>
+          <t>-0,58; 0,71</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,46; 1,3</t>
+          <t>0,32; 2,0</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,87; 0,38</t>
+          <t>0,0; 1,49</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,53; 1,19</t>
+          <t>0,7; 2,64</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,1; 1,28</t>
+          <t>0,11; 1,21</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -1365,7 +1365,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,2; 1,53</t>
+          <t>0,17; 1,28</t>
         </is>
       </c>
     </row>
@@ -1378,34 +1378,34 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>80,15%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-43,6%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>3,25%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>inf%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>inf%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>inf%</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>80,15%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>-43,6%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>45,55%</t>
-        </is>
-      </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
           <t>342,58%</t>
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>442,67%</t>
+          <t>397,19%</t>
         </is>
       </c>
     </row>
@@ -1461,7 +1461,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-57,42; —</t>
+          <t>-61,01; —</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-19,06; —</t>
+          <t>-18,61; —</t>
         </is>
       </c>
     </row>
